--- a/output/graficos_dimensiones/comunal_d_env_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:29</t>
+    <t xml:space="preserve">2026-09-12 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:41</t>
+    <t xml:space="preserve">2026-09-24 00:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -514,7 +514,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>113.84</v>
+        <v>123.04</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>108.97</v>
+        <v>117.07</v>
       </c>
     </row>
     <row r="4">
@@ -548,7 +548,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>107.05</v>
+        <v>115.06</v>
       </c>
     </row>
     <row r="5">
@@ -565,7 +565,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>106.24</v>
+        <v>113.89</v>
       </c>
     </row>
     <row r="6">
@@ -582,7 +582,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>105.9</v>
+        <v>113.31</v>
       </c>
     </row>
     <row r="7">
@@ -599,7 +599,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>100.19</v>
+        <v>107.59</v>
       </c>
     </row>
     <row r="8">
@@ -616,7 +616,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>96.34</v>
+        <v>103.32</v>
       </c>
     </row>
     <row r="9">
@@ -633,7 +633,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>95.58</v>
+        <v>102.68</v>
       </c>
     </row>
     <row r="10">
@@ -650,7 +650,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>95.55</v>
+        <v>102.32</v>
       </c>
     </row>
     <row r="11">
@@ -667,7 +667,7 @@
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>92.24</v>
+        <v>98.98</v>
       </c>
     </row>
     <row r="12">
@@ -684,7 +684,7 @@
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>81.87</v>
+        <v>87.68</v>
       </c>
     </row>
     <row r="13">
@@ -701,7 +701,7 @@
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>75.43</v>
+        <v>81.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:09</t>
+    <t xml:space="preserve">2026-10-02 16:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:15</t>
+    <t xml:space="preserve">2026-10-05 16:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
